--- a/docs/ui-identity-eight/KyIdentity-Council.xlsx
+++ b/docs/ui-identity-eight/KyIdentity-Council.xlsx
@@ -27774,7 +27774,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"web_unit": {"status": "pass", "count": 198, "evidence": "checks/r2-web-unit.txt"}, "web_build": {"status": "pass", "evidence": "checks/r2-web-build.txt", "advisory": "Vite reports a &gt;500kB uncompressed bundle; emitted gzip is150.91kB. No compiler/typecheck failure; no claim of a new performance optimization."}, "browser": {"status": "pass", "cases": 4, "evidence": "checks/r2-browser.json", "scope": "Desktop/phone\u00d7light/dark: stable row geometry, viewport-contained native popover, one open, keyboard/outside dismissal, focus return including Edit dialog, truthful empty state/search, full policy retained and40px Security controls."}, "impeccable": {"status": "pass", "findings": 0, "evidence": "checks/r2-impeccable.json", "note": "Rerun after the explicit native-anchor cleanup; no findings."}, "full_required": {"status": "running", "results": "checks/r2-results.json", "source_commit": "0e5cee3", "scope": "Initial full suite started before desktop-only CSS anchor cleanup. Final-source hosted CI must validate current head; never represent old embedding as freshly tested final source."}}</t>
+          <t xml:space="preserve">{"web_unit": {"status": "pass", "count": 198, "evidence": "checks/r2-web-unit.txt"}, "web_build": {"status": "pass", "evidence": "checks/r2-web-build.txt", "advisory": "Vite reports a &gt;500kB uncompressed bundle; emitted gzip is150.91kB. No compiler/typecheck failure; no claim of a new performance optimization."}, "browser": {"status": "pass", "cases": 4, "evidence": "checks/r2-browser.json", "scope": "Desktop/phone\u00d7light/dark: stable row geometry, viewport-contained native popover, one open, keyboard/outside dismissal, focus return including Edit dialog, truthful empty state/search, full policy retained and40px Security controls."}, "impeccable": {"status": "pass", "findings": 0, "evidence": "checks/r2-impeccable.json", "note": "Rerun after the explicit native-anchor cleanup; no findings."}, "full_required": {"status": "pass_with_source_provenance_limit", "results": "checks/r2-results.json", "source_commit": "0e5cee3", "scope": "All eight local groups passed. The runner captured source_commit once at start, before final desktop CSS cleanup. Later groups used the then-current worktree; exact per-group source was not recorded. Treat result source_commit fields as runner-start provenance, not an attestation of every executed file. Final-head hosted CI and security still required.", "groups": 8, "runner_start_commit": "0e5cee3128072ccd7d71a9674e5a944cd157127a", "evidence_sha256": {"r2-toolchain.txt": "25e6e8e364358b7ae7fbff887a8752e9c0264caa2231886b25f1870caad2b311", "r2-race.txt": "d9bbd151f1eac02564547784be1b663c1f4d72dc1e881acc828913a3b751b112", "r2-fips-race.txt": "db9782394bd5dad350fbe0fd5f086150c6f43fb30fb3f874b0e5e781c29ce640", "r2-web.txt": "ab3689cc879288ee50a938ec2ae172fed5c8f9c302658c91ac39ca68b3b9f366", "r2-workers.txt": "c88f8c4561a75e321270fa24673c4ef330859e26a89ddd5871ca951ea1d5011e", "r2-vulnerabilities.txt": "1d875b2fec09906ad73046db10d006fa84b6d17aeb6fd3a9539e1798ff975cb0", "r2-repeatable.txt": "69959d4124e6570965906cd0a9de3f37469ee32867e9cafe651c64f4e5a30505", "r2-docker.txt": "29405584ea54babffdadb73fd4ac22ed0af9e1672a521241a7655741dde5ecd3"}}}</t>
         </is>
       </c>
     </row>
